--- a/Squad 1/Dados brutos/Aluno Lucas Maia/projetos_minerais_goias.xlsx
+++ b/Squad 1/Dados brutos/Aluno Lucas Maia/projetos_minerais_goias.xlsx
@@ -1699,12 +1699,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>AngloGold Ashanti</t>
+          <t>Aura Minerals</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>AngloGold Ashanti plc</t>
+          <t>Aura Minerals Inc.</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -1804,7 +1804,7 @@
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>2024-02-15</t>
+          <t>2025-12-01</t>
         </is>
       </c>
       <c r="Y9" t="inlineStr">
@@ -1829,17 +1829,17 @@
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>Venda anunciada pela AngloGold Ashanti em 02/06/2025; fechamento da aquisição informado pela Aura em 01/12/2025</t>
         </is>
       </c>
       <c r="AD9" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>https://www.auraminerals.com/investors/</t>
         </is>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
-          <t>Uma das frentes operacionais de ouro mais longevas do Brasil, com expansão constante de frentes subterrâneas profundas.</t>
+          <t>Uma das frentes operacionais de ouro mais longevas do Brasil, com expansão constante de frentes subterrâneas profundas. Operada pela AngloGold Ashanti até 11/2025; desde 01/12/2025 pertence à Aura Minerals. A evidência principal e a produção de 80.000 oz/ano são do período AngloGold (relatório de 2024).</t>
         </is>
       </c>
     </row>

--- a/Squad 1/Dados brutos/Aluno Lucas Maia/projetos_minerais_goias.xlsx
+++ b/Squad 1/Dados brutos/Aluno Lucas Maia/projetos_minerais_goias.xlsx
@@ -882,7 +882,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>https://www.hochschildmining.com/</t>
+          <t>https://www.investegate.co.uk/announcement/rns/hochschild-mining--hoc/commercial-production-achieved-at-mara-rosa/8193903</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
@@ -1039,7 +1039,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>https://serraverde.com/</t>
+          <t>https://www.serraverde.com/2024/01/serra-verde-enters-commercial-production/</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
@@ -1196,7 +1196,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>https://www.aclara-re.com/</t>
+          <t>https://cdn.prod.website-files.com/65bc531432a98553cc63c479/65bc531432a98553cc63c70b_PR_Carina%20Module_PEA%20VF_clean_2.pdf</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
@@ -1353,7 +1353,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>https://www.angloamerican.com</t>
+          <t>https://www.angloamerican.com/media/press-releases/2024/08-02-2024</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
@@ -1510,7 +1510,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>https://cmocbrasil.com/</t>
+          <t>https://www1.hkexnews.hk/listedco/listconews/sehk/2024/0322/2024032201879.pdf</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
@@ -1667,7 +1667,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>https://alvominerals.com/</t>
+          <t>https://www.marketindex.com.au/asx/alv/announcements/high-grade-copper-zinc-intersected-at-c4-prospect-3A641114</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
@@ -1824,7 +1824,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>https://www.anglogoldashanti.com</t>
+          <t>https://reports.anglogoldashanti.com/23/wp-content/uploads/2024/04/AGA-OP23-SERRA-GRANDE.pdf</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
@@ -1991,7 +1991,7 @@
       </c>
       <c r="AD10" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>https://www.equinoxgold.com/wp-content/uploads/2023/02/20210419-EQX-PR-PilarSale.pdf</t>
         </is>
       </c>
       <c r="AE10" t="inlineStr">
@@ -2138,7 +2138,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>https://valor.globo.com</t>
+          <t>https://api.mziq.com/mzfilemanager/v2/d/73a23c6c-b1fd-4abb-beba-056de474f2ec/646cc0f8-cbbe-ca64-c300-cff0fcb0372a?origin=1</t>
         </is>
       </c>
       <c r="AC11" t="inlineStr">
@@ -2148,7 +2148,7 @@
       </c>
       <c r="AD11" t="inlineStr">
         <is>
-          <t>https://cba.com.br</t>
+          <t>NA</t>
         </is>
       </c>
       <c r="AE11" t="inlineStr">
@@ -3188,7 +3188,7 @@
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>https://www.hochschildmining.com/</t>
+          <t>https://www.mining.com/hochschilds-mara-rosa-gold-mine-reaches-commercial-production/</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
@@ -3270,7 +3270,7 @@
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>https://www.aclara-re.com/</t>
+          <t>https://cdn.prod.website-files.com/65bc531432a98553cc63c479/65bc531432a98553cc63c70b_PR_Carina%20Module_PEA%20VF_clean_2.pdf</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
@@ -3352,7 +3352,7 @@
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>https://alvominerals.com/</t>
+          <t>https://www.marketindex.com.au/asx/alv/announcements/high-grade-copper-zinc-intersected-at-c4-prospect-3A641114</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
